--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.86298083888654</v>
+        <v>6.477734386319062</v>
       </c>
       <c r="D2" t="n">
-        <v>38.33995485659285</v>
+        <v>6.230242664196338</v>
       </c>
       <c r="E2" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F2" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.51344384851378</v>
+        <v>5.60843462538349</v>
       </c>
       <c r="D3" t="n">
-        <v>31.97593311464115</v>
+        <v>5.196089131129186</v>
       </c>
       <c r="E3" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F3" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.65110470450959</v>
+        <v>4.980804514482809</v>
       </c>
       <c r="D4" t="n">
-        <v>28.53113781895072</v>
+        <v>4.636309895579492</v>
       </c>
       <c r="E4" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F4" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.00216755293555</v>
+        <v>3.900352227352027</v>
       </c>
       <c r="D5" t="n">
-        <v>22.01618925081997</v>
+        <v>3.577630753258245</v>
       </c>
       <c r="E5" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F5" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.59863726054562</v>
+        <v>6.272278554838663</v>
       </c>
       <c r="D6" t="n">
-        <v>25.40386064333611</v>
+        <v>4.128127354542118</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F6" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.88077362208228</v>
+        <v>3.71812571358837</v>
       </c>
       <c r="D7" t="n">
-        <v>19.89250677020409</v>
+        <v>3.232532350158164</v>
       </c>
       <c r="E7" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F7" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.77856301022953</v>
+        <v>2.889016489162298</v>
       </c>
       <c r="D8" t="n">
-        <v>17.05445677116934</v>
+        <v>2.771349225315018</v>
       </c>
       <c r="E8" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F8" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.40975934357997</v>
+        <v>5.429085893331745</v>
       </c>
       <c r="D9" t="n">
-        <v>32.71000545671011</v>
+        <v>5.315375886715394</v>
       </c>
       <c r="E9" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F9" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.70653359183294</v>
+        <v>3.852311708672854</v>
       </c>
       <c r="D10" t="n">
-        <v>6.694772748455907</v>
+        <v>1.087900571624085</v>
       </c>
       <c r="E10" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F10" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.71208300631562</v>
+        <v>5.640713488526288</v>
       </c>
       <c r="D11" t="n">
-        <v>35.54954502874124</v>
+        <v>5.776801067170451</v>
       </c>
       <c r="E11" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F11" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.42921723418985</v>
+        <v>6.732247800555851</v>
       </c>
       <c r="D12" t="n">
-        <v>23.7030128786166</v>
+        <v>3.851739592775199</v>
       </c>
       <c r="E12" t="n">
-        <v>7.507440681469097</v>
+        <v>1.219959110738728</v>
       </c>
       <c r="F12" t="n">
-        <v>8.741643315473359</v>
+        <v>1.420517038764421</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
